--- a/VerveStacks_KEN/SysSettings.xlsx
+++ b/VerveStacks_KEN/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9C4CF5-6257-4050-8675-A3D75FBA16CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6019AF2F-427D-40D9-871B-03CE64A65309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="344">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -677,6 +677,24 @@
   </si>
   <si>
     <t>cap_bnd</t>
+  </si>
+  <si>
+    <t>~tfm_comgrp</t>
+  </si>
+  <si>
+    <t>allregions</t>
+  </si>
+  <si>
+    <t>cset_cn</t>
+  </si>
+  <si>
+    <t>ELC,e[_]*</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>ELC_BatIn</t>
   </si>
   <si>
     <t>KEN</t>
@@ -3442,7 +3460,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -3525,7 +3543,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -3557,10 +3575,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="O5" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -3569,7 +3587,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -3586,10 +3604,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="O6" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -3598,7 +3616,7 @@
         <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -3615,10 +3633,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="O7" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -3627,7 +3645,7 @@
         <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -3644,10 +3662,10 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="O8" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -3656,7 +3674,7 @@
         <v>35</v>
       </c>
       <c r="R8" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="2:18">
@@ -3673,10 +3691,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="O9" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -3685,7 +3703,7 @@
         <v>35</v>
       </c>
       <c r="R9" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="2:18">
@@ -3702,10 +3720,10 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="O10" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -3714,7 +3732,7 @@
         <v>35</v>
       </c>
       <c r="R10" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="2:18">
@@ -3731,10 +3749,10 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="O11" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -3743,7 +3761,7 @@
         <v>35</v>
       </c>
       <c r="R11" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="2:18">
@@ -3760,10 +3778,10 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="O12" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -3772,7 +3790,7 @@
         <v>35</v>
       </c>
       <c r="R12" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="2:18">
@@ -3789,10 +3807,10 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="O13" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="P13" t="s">
         <v>25</v>
@@ -3801,7 +3819,7 @@
         <v>35</v>
       </c>
       <c r="R13" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="2:18">
@@ -3821,10 +3839,10 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O14" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
@@ -3833,7 +3851,7 @@
         <v>35</v>
       </c>
       <c r="R14" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="2:18">
@@ -3853,10 +3871,10 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="O15" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -3865,7 +3883,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="2:18">
@@ -3894,10 +3912,10 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="O16" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -3906,7 +3924,7 @@
         <v>35</v>
       </c>
       <c r="R16" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="2:18">
@@ -3926,10 +3944,10 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="O17" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -3938,7 +3956,7 @@
         <v>35</v>
       </c>
       <c r="R17" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="2:18">
@@ -3958,10 +3976,10 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="O18" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -3970,7 +3988,7 @@
         <v>35</v>
       </c>
       <c r="R18" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="2:18">
@@ -3990,10 +4008,10 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="O19" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -4002,7 +4020,7 @@
         <v>35</v>
       </c>
       <c r="R19" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="2:18">
@@ -4022,10 +4040,10 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="O20" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
@@ -4034,7 +4052,7 @@
         <v>35</v>
       </c>
       <c r="R20" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="2:18">
@@ -4060,10 +4078,10 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="O21" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -4072,7 +4090,7 @@
         <v>35</v>
       </c>
       <c r="R21" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="2:18">
@@ -4092,10 +4110,10 @@
         <v>17</v>
       </c>
       <c r="N22" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="P22" t="s">
         <v>25</v>
@@ -4104,7 +4122,7 @@
         <v>35</v>
       </c>
       <c r="R22" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="2:18">
@@ -4121,10 +4139,10 @@
         <v>17</v>
       </c>
       <c r="N23" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="O23" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="P23" t="s">
         <v>25</v>
@@ -4133,7 +4151,7 @@
         <v>35</v>
       </c>
       <c r="R23" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="2:18">
@@ -4150,10 +4168,10 @@
         <v>17</v>
       </c>
       <c r="N24" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="O24" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="P24" t="s">
         <v>25</v>
@@ -4162,7 +4180,7 @@
         <v>35</v>
       </c>
       <c r="R24" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="2:18">
@@ -4170,10 +4188,10 @@
         <v>17</v>
       </c>
       <c r="N25" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="O25" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
@@ -4182,7 +4200,7 @@
         <v>35</v>
       </c>
       <c r="R25" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="2:18">
@@ -4190,10 +4208,10 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="O26" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="P26" t="s">
         <v>25</v>
@@ -4202,7 +4220,7 @@
         <v>35</v>
       </c>
       <c r="R26" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="2:18">
@@ -4210,10 +4228,10 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="O27" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="P27" t="s">
         <v>25</v>
@@ -4222,18 +4240,23 @@
         <v>35</v>
       </c>
       <c r="R27" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" ht="17.649999999999999" thickBot="1">
+      <c r="B28" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
       <c r="M28" t="s">
         <v>17</v>
       </c>
       <c r="N28" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="O28" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="P28" t="s">
         <v>25</v>
@@ -4242,18 +4265,27 @@
         <v>35</v>
       </c>
       <c r="R28" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" ht="15" thickTop="1" thickBot="1">
+      <c r="B29" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="M29" t="s">
         <v>17</v>
       </c>
       <c r="N29" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="O29" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -4262,18 +4294,27 @@
         <v>35</v>
       </c>
       <c r="R29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="B30" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="30" spans="2:18">
+      <c r="D30" t="s">
+        <v>216</v>
+      </c>
       <c r="M30" t="s">
         <v>17</v>
       </c>
       <c r="N30" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="O30" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="P30" t="s">
         <v>25</v>
@@ -4282,7 +4323,7 @@
         <v>35</v>
       </c>
       <c r="R30" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="2:18">
@@ -4290,10 +4331,10 @@
         <v>17</v>
       </c>
       <c r="N31" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="O31" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="P31" t="s">
         <v>25</v>
@@ -4302,7 +4343,7 @@
         <v>35</v>
       </c>
       <c r="R31" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="2:18">
@@ -4310,10 +4351,10 @@
         <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="O32" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="P32" t="s">
         <v>25</v>
@@ -4322,7 +4363,7 @@
         <v>35</v>
       </c>
       <c r="R32" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="13:18">
@@ -4330,10 +4371,10 @@
         <v>17</v>
       </c>
       <c r="N33" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="O33" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="P33" t="s">
         <v>25</v>
@@ -4342,7 +4383,7 @@
         <v>35</v>
       </c>
       <c r="R33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="13:18">
@@ -4350,10 +4391,10 @@
         <v>17</v>
       </c>
       <c r="N34" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="O34" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="P34" t="s">
         <v>25</v>
@@ -4362,7 +4403,7 @@
         <v>35</v>
       </c>
       <c r="R34" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="13:18">
@@ -4370,10 +4411,10 @@
         <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="O35" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="P35" t="s">
         <v>25</v>
@@ -4382,7 +4423,7 @@
         <v>35</v>
       </c>
       <c r="R35" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="13:18">
@@ -4390,10 +4431,10 @@
         <v>17</v>
       </c>
       <c r="N36" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="O36" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="P36" t="s">
         <v>25</v>
@@ -4402,7 +4443,7 @@
         <v>35</v>
       </c>
       <c r="R36" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="13:18">
@@ -4410,10 +4451,10 @@
         <v>17</v>
       </c>
       <c r="N37" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="O37" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="P37" t="s">
         <v>25</v>
@@ -4422,7 +4463,7 @@
         <v>35</v>
       </c>
       <c r="R37" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="13:18">
@@ -4430,10 +4471,10 @@
         <v>17</v>
       </c>
       <c r="N38" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="O38" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="P38" t="s">
         <v>25</v>
@@ -4442,7 +4483,7 @@
         <v>35</v>
       </c>
       <c r="R38" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="13:18">
@@ -4450,10 +4491,10 @@
         <v>17</v>
       </c>
       <c r="N39" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="O39" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="P39" t="s">
         <v>25</v>
@@ -4462,7 +4503,7 @@
         <v>35</v>
       </c>
       <c r="R39" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="13:18">
@@ -4470,10 +4511,10 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="O40" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="P40" t="s">
         <v>25</v>
@@ -4482,7 +4523,7 @@
         <v>35</v>
       </c>
       <c r="R40" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="13:18">
@@ -4490,10 +4531,10 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="O41" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="P41" t="s">
         <v>25</v>
@@ -4502,7 +4543,7 @@
         <v>35</v>
       </c>
       <c r="R41" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="13:18">
@@ -4510,10 +4551,10 @@
         <v>17</v>
       </c>
       <c r="N42" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="O42" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="P42" t="s">
         <v>25</v>
@@ -4522,7 +4563,7 @@
         <v>35</v>
       </c>
       <c r="R42" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="13:18">
@@ -4530,10 +4571,10 @@
         <v>17</v>
       </c>
       <c r="N43" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="O43" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="P43" t="s">
         <v>25</v>
@@ -4542,7 +4583,7 @@
         <v>35</v>
       </c>
       <c r="R43" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="13:18">
@@ -4550,10 +4591,10 @@
         <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="O44" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="P44" t="s">
         <v>25</v>
@@ -4562,7 +4603,7 @@
         <v>35</v>
       </c>
       <c r="R44" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="13:18">
@@ -4570,10 +4611,10 @@
         <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="O45" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="P45" t="s">
         <v>25</v>
@@ -4582,7 +4623,7 @@
         <v>35</v>
       </c>
       <c r="R45" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="13:18">
@@ -4590,10 +4631,10 @@
         <v>17</v>
       </c>
       <c r="N46" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="O46" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="P46" t="s">
         <v>25</v>
@@ -4602,7 +4643,7 @@
         <v>35</v>
       </c>
       <c r="R46" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="13:18">
@@ -4610,10 +4651,10 @@
         <v>17</v>
       </c>
       <c r="N47" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="O47" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="P47" t="s">
         <v>25</v>
@@ -4622,7 +4663,7 @@
         <v>35</v>
       </c>
       <c r="R47" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="13:18">
@@ -4630,10 +4671,10 @@
         <v>17</v>
       </c>
       <c r="N48" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="O48" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="P48" t="s">
         <v>25</v>
@@ -4642,7 +4683,7 @@
         <v>35</v>
       </c>
       <c r="R48" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="13:18">
@@ -4650,10 +4691,10 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="O49" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="P49" t="s">
         <v>25</v>
@@ -4662,7 +4703,7 @@
         <v>35</v>
       </c>
       <c r="R49" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="13:18">
@@ -4670,10 +4711,10 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="O50" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="P50" t="s">
         <v>25</v>
@@ -4682,7 +4723,7 @@
         <v>35</v>
       </c>
       <c r="R50" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="13:18">
@@ -4690,10 +4731,10 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="O51" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="P51" t="s">
         <v>25</v>
@@ -4702,7 +4743,7 @@
         <v>35</v>
       </c>
       <c r="R51" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="13:18">
@@ -4710,10 +4751,10 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="O52" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="P52" t="s">
         <v>25</v>
@@ -4722,7 +4763,7 @@
         <v>35</v>
       </c>
       <c r="R52" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="13:18">
@@ -4730,10 +4771,10 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="O53" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="P53" t="s">
         <v>25</v>
@@ -4742,7 +4783,7 @@
         <v>35</v>
       </c>
       <c r="R53" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="13:18">
@@ -4750,10 +4791,10 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="O54" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="P54" t="s">
         <v>25</v>
@@ -4762,7 +4803,7 @@
         <v>35</v>
       </c>
       <c r="R54" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="13:18">
@@ -4770,10 +4811,10 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O55" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P55" t="s">
         <v>25</v>
@@ -4782,7 +4823,7 @@
         <v>35</v>
       </c>
       <c r="R55" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="13:18">
@@ -4790,10 +4831,10 @@
         <v>17</v>
       </c>
       <c r="N56" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="O56" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="P56" t="s">
         <v>25</v>
@@ -4802,7 +4843,7 @@
         <v>35</v>
       </c>
       <c r="R56" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="13:18">
@@ -4810,10 +4851,10 @@
         <v>17</v>
       </c>
       <c r="N57" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="O57" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="P57" t="s">
         <v>25</v>
@@ -4822,7 +4863,7 @@
         <v>35</v>
       </c>
       <c r="R57" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="13:18">
@@ -4830,10 +4871,10 @@
         <v>17</v>
       </c>
       <c r="N58" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="O58" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="P58" t="s">
         <v>25</v>
@@ -4842,7 +4883,7 @@
         <v>35</v>
       </c>
       <c r="R58" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="13:18">
@@ -4850,10 +4891,10 @@
         <v>17</v>
       </c>
       <c r="N59" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="O59" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="P59" t="s">
         <v>25</v>
@@ -4862,7 +4903,7 @@
         <v>35</v>
       </c>
       <c r="R59" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="13:18">
@@ -4870,10 +4911,10 @@
         <v>17</v>
       </c>
       <c r="N60" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="O60" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="P60" t="s">
         <v>25</v>
@@ -4882,7 +4923,7 @@
         <v>35</v>
       </c>
       <c r="R60" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="13:18">
@@ -4890,10 +4931,10 @@
         <v>17</v>
       </c>
       <c r="N61" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="O61" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="P61" t="s">
         <v>25</v>
@@ -4902,7 +4943,7 @@
         <v>35</v>
       </c>
       <c r="R61" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="13:18">
@@ -4910,10 +4951,10 @@
         <v>17</v>
       </c>
       <c r="N62" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="O62" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="P62" t="s">
         <v>25</v>
@@ -4922,7 +4963,7 @@
         <v>35</v>
       </c>
       <c r="R62" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" spans="13:18">
@@ -4930,10 +4971,10 @@
         <v>17</v>
       </c>
       <c r="N63" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="O63" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="P63" t="s">
         <v>25</v>
@@ -4942,7 +4983,7 @@
         <v>35</v>
       </c>
       <c r="R63" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64" spans="13:18">
@@ -4950,10 +4991,10 @@
         <v>17</v>
       </c>
       <c r="N64" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="O64" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="P64" t="s">
         <v>25</v>
@@ -4962,7 +5003,7 @@
         <v>35</v>
       </c>
       <c r="R64" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="13:18">
@@ -4970,10 +5011,10 @@
         <v>17</v>
       </c>
       <c r="N65" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="O65" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="P65" t="s">
         <v>25</v>
@@ -4982,7 +5023,7 @@
         <v>35</v>
       </c>
       <c r="R65" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
